--- a/campanas/260505_ilocalizables/listado.xlsx
+++ b/campanas/260505_ilocalizables/listado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diegopaezmacias/GRIDDED.AGENCY local/00_GRIDDED AGENCY/cdn/campanas/260505_ilocalizables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11DDEC3-9209-5943-B9AC-426428C92576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7C4B13-197E-DC43-8BE4-A616B35F73BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="800" yWindow="600" windowWidth="34820" windowHeight="23020" xr2:uid="{5E218A98-A45B-6E40-B200-9B38D51E9F92}"/>
   </bookViews>
@@ -5882,7 +5882,7 @@
         <v>1792</v>
       </c>
       <c r="D2" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="E2" t="s">
         <v>1808</v>

--- a/campanas/260505_ilocalizables/listado.xlsx
+++ b/campanas/260505_ilocalizables/listado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diegopaezmacias/GRIDDED.AGENCY local/00_GRIDDED AGENCY/cdn/campanas/260505_ilocalizables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7C4B13-197E-DC43-8BE4-A616B35F73BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188DD0CD-A833-2D43-8E0D-8FA950F961AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="800" yWindow="600" windowWidth="34820" windowHeight="23020" xr2:uid="{5E218A98-A45B-6E40-B200-9B38D51E9F92}"/>
   </bookViews>
@@ -5899,7 +5899,7 @@
         <v>1793</v>
       </c>
       <c r="D3" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="E3" t="s">
         <v>1808</v>
@@ -5916,7 +5916,7 @@
         <v>1794</v>
       </c>
       <c r="D4" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="E4" t="s">
         <v>1808</v>
@@ -5933,7 +5933,7 @@
         <v>1795</v>
       </c>
       <c r="D5" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="E5" t="s">
         <v>1808</v>
@@ -5950,7 +5950,7 @@
         <v>1796</v>
       </c>
       <c r="D6" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="E6" t="s">
         <v>1808</v>
@@ -5967,7 +5967,7 @@
         <v>1797</v>
       </c>
       <c r="D7" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="E7" t="s">
         <v>1808</v>
@@ -5984,7 +5984,7 @@
         <v>1798</v>
       </c>
       <c r="D8" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="E8" t="s">
         <v>1808</v>
@@ -6001,7 +6001,7 @@
         <v>1799</v>
       </c>
       <c r="D9" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="E9" t="s">
         <v>1808</v>
@@ -6018,7 +6018,7 @@
         <v>1800</v>
       </c>
       <c r="D10" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="E10" t="s">
         <v>1808</v>
@@ -6035,7 +6035,7 @@
         <v>1801</v>
       </c>
       <c r="D11" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="E11" t="s">
         <v>1808</v>
@@ -6052,7 +6052,7 @@
         <v>1802</v>
       </c>
       <c r="D12" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="E12" t="s">
         <v>1808</v>
@@ -6069,7 +6069,7 @@
         <v>1803</v>
       </c>
       <c r="D13" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="E13" t="s">
         <v>1808</v>
@@ -6086,7 +6086,7 @@
         <v>1804</v>
       </c>
       <c r="D14" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="E14" t="s">
         <v>1808</v>
@@ -6103,7 +6103,7 @@
         <v>1805</v>
       </c>
       <c r="D15" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="E15" t="s">
         <v>1808</v>
@@ -6120,7 +6120,7 @@
         <v>1806</v>
       </c>
       <c r="D16" s="1">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="E16" t="s">
         <v>1808</v>

--- a/campanas/260505_ilocalizables/listado.xlsx
+++ b/campanas/260505_ilocalizables/listado.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diegopaezmacias/GRIDDED.AGENCY local/00_GRIDDED AGENCY/cdn/campanas/260505_ilocalizables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188DD0CD-A833-2D43-8E0D-8FA950F961AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3E9AE7-F98A-3B49-BAC3-695E74370C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="800" yWindow="600" windowWidth="34820" windowHeight="23020" xr2:uid="{5E218A98-A45B-6E40-B200-9B38D51E9F92}"/>
+    <workbookView xWindow="800" yWindow="600" windowWidth="18720" windowHeight="23020" xr2:uid="{5E218A98-A45B-6E40-B200-9B38D51E9F92}"/>
   </bookViews>
   <sheets>
     <sheet name="ilocalizables_limpio" sheetId="1" r:id="rId1"/>
@@ -8856,9 +8856,6 @@
       <c r="C177">
         <v>161</v>
       </c>
-      <c r="D177" s="1">
-        <v>46149</v>
-      </c>
       <c r="E177" t="s">
         <v>1809</v>
       </c>
@@ -8873,9 +8870,6 @@
       <c r="C178">
         <v>162</v>
       </c>
-      <c r="D178" s="1">
-        <v>46149</v>
-      </c>
       <c r="E178" t="s">
         <v>1809</v>
       </c>
@@ -8890,9 +8884,6 @@
       <c r="C179">
         <v>163</v>
       </c>
-      <c r="D179" s="1">
-        <v>46149</v>
-      </c>
       <c r="E179" t="s">
         <v>1809</v>
       </c>
@@ -8907,9 +8898,6 @@
       <c r="C180">
         <v>164</v>
       </c>
-      <c r="D180" s="1">
-        <v>46149</v>
-      </c>
       <c r="E180" t="s">
         <v>1809</v>
       </c>
@@ -8924,9 +8912,6 @@
       <c r="C181">
         <v>165</v>
       </c>
-      <c r="D181" s="1">
-        <v>46149</v>
-      </c>
       <c r="E181" t="s">
         <v>1809</v>
       </c>
@@ -8941,9 +8926,6 @@
       <c r="C182">
         <v>166</v>
       </c>
-      <c r="D182" s="1">
-        <v>46149</v>
-      </c>
       <c r="E182" t="s">
         <v>1809</v>
       </c>
@@ -8958,9 +8940,6 @@
       <c r="C183">
         <v>167</v>
       </c>
-      <c r="D183" s="1">
-        <v>46149</v>
-      </c>
       <c r="E183" t="s">
         <v>1809</v>
       </c>
@@ -8975,9 +8954,6 @@
       <c r="C184">
         <v>168</v>
       </c>
-      <c r="D184" s="1">
-        <v>46149</v>
-      </c>
       <c r="E184" t="s">
         <v>1809</v>
       </c>
@@ -8991,9 +8967,6 @@
       </c>
       <c r="C185">
         <v>169</v>
-      </c>
-      <c r="D185" s="1">
-        <v>46149</v>
       </c>
       <c r="E185" t="s">
         <v>1809</v>
